--- a/Result/checksun_type/農藥.xlsx
+++ b/Result/checksun_type/農藥.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>91.35999999999999</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>96.48</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>104.24</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>96.48</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>104.24</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>33676529.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>17636975.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>17636975.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>12592457.9</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>9778256.84</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>9778256.84</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>2772861.329213161</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>33676529</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>33676529.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>92.28</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>97.28</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>104.7</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>97.28</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>104.7</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>40083950.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>13344322.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>13344322.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>10361183.3</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>9271574.16</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>9271574.16</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>1481458.574324042</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>40083950</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>40083950.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>93.0</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>98.08</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>105.16</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>98.08</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>105.16</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>4631599.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>5868730.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>5868730.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>10848722.6</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>9162061.72</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>9162061.720000001</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1102821.131743413</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>4631599</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>4631599.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>93.32</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>98.82</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>105.71</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>98.81999999999999</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>105.71</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>3922854.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>6002952.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>6002952</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>11056227.7</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>9308342.3</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>9308342.300000001</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-956796.6357060838</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>3922854</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>3922854.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>93.68</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>99.7</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>106.24</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>106.24</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>5869947.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>5991063.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>5991063.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>11363922.3</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>9882547.34</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>9882547.34</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-638081.940091826</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>5869947</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>5869947.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>93.46000000000001</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>100.3</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>106.7</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>106.7</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>12213261.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>7547940.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>7547940</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>11664508.1</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>9970586.78</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>9970586.779999999</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-368603.6984967496</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>12213261</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>12213261.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>93.96000000000001</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>100.89</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>107.08</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>100.89</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>107.08</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>2705993.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>7378044.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>7378044.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>12987374.2</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>10179667.62</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>10179667.62</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-650111.1498431861</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>2705993</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>2705993.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>93.72</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>101.53</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>107.57</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>101.53</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>107.57</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>5302705.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>15828714.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>15828714.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>13329079.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>10333114.7</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>10333114.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-10410.53927226551</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>5302705</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>5302705.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>94.84</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>102.24</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>108.05</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>102.24</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>108.05</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>3863413.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>16109503.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>16109503.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>13119123.2</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>10506274.58</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>10506274.58</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>625600.1379459128</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>3863413</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>3863413.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>96.04</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>102.78</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>108.54</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>102.78</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>108.54</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>13654328.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>16736780.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>16736780.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>13653981.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>10677228.06</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>10677228.06</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>1666053.814759528</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>13654328</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>13654328.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>97.52</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>103.38</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>109.06</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>103.38</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>109.06</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>11363783.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>15781076.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>15781076.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>13070155.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>10774485.02</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>10774485.02</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>2043887.681108998</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>11363783</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>11363783.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>34.27</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>32.35</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>32.64</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>32.64</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>30752.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>26021.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>26021.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>27135.3</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>14215.12</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>14215.12</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>1676.657039741152</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>30752</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>30752.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>33.98</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>32.19</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>32.61</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>32.19</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>32.61</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>15599.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>23408.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>23408.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>25268.3</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>14319.64</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>14319.64</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>1114.689186374952</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>15599</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>15599.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>33.77</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>32.07</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>32.62</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>32.07</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>32.62</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>9517.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>24723.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>24723.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>24634.6</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>14301.02</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>14301.02</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>1895.603353481278</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>9517</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>9517.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>33.68</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>31.99</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>32.64</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>31.99</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>32.64</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>31971.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>27396.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>27396</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>24460.1</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>14465.96</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>14465.96</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>3595.137758151694</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>31971</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>31971.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>33.58</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>31.91</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>32.67</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>32.67</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>42270.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>26727.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>26727.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>22014.3</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>14159.48</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>14159.48</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>3488.860559175446</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>42270</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>42270.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>33.34</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>31.81</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>32.67</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>32.67</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>17685.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>28248.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>28248.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>18790.2</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>13569.2</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>13569.2</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>2108.9695406674</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>17685</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>17685.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>32.92999999999999</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>31.75</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>32.7</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>32.7</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>22175.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>27128.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>27128.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>17701.2</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>13365.52</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>13365.52</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>2696.4834592035</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>22175</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>22175.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>32.44</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>31.71</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>32.72</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>32.72</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>22879.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>24545.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>24545.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>16522.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>13109.9</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>13109.9</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>2958.414647854945</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>22879</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>22879.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>31.82</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>31.66</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>32.74</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>32.74</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>28629.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>21524.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>21524.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>15788.2</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>12943.64</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>12943.64</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>3151.51582279076</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>28629</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>28629.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>31.32999999999999</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>31.61</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>32.78</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>32.78</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>49876.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>17301.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>17301</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>13897.0</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>12734.7</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>12734.7</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>2698.74907902797</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>49876</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>49876.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>30.82</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>32.8</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>12082.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>9331.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>9331.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>10294.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>11920.4</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>11920.4</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-320.9087363127292</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>12082</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>12082.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>23.62</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>24.01</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>24.32</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>24.32</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>352.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>1242.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>1242.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>1186.1</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>1036.92</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>1036.92</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-14.4107574645036</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>352</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>352.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>23.6</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>24.05</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>24.33</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>24.33</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>1197.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>1512.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>1512.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>1221.0</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>1171.82</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>1171.82</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>57.71011528706072</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>1197</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>1197.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>23.64</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>24.12</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>24.36</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>24.36</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>492.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>1485.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>1485</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>1183.5</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>1160.4</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>1160.4</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>68.14314367190059</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>492</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>492.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>23.72</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>24.19</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>24.4</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>1452.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>1517.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>1517.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>1182.5</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>1169.96</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>1169.96</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>156.1495005191039</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>1452</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>1452.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>23.79</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>24.28</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>24.44</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>24.28</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>24.44</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>2720.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>1440.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>1440</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>1219.4</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>1144.44</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>1144.44</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>173.4389567108549</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>2720</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>2720.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>23.88</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>24.32</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>24.47</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>24.47</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>1700.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>1129.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>1129.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>996.7</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>1096.88</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>1096.88</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>56.08678853082563</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>1700</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>1700.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>23.89</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>24.34</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>24.5</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>24.5</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>1061.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>929.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>929.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>911.1</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>1083.12</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>1083.12</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-4.276551316745554</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>1061</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>1061.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>23.9</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>24.36</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>24.53</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>24.36</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>24.53</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>654.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>882.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>882</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>835.9</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>1093.62</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>1093.62</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-21.89287426624901</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>654</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>654.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>23.91</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>24.38</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>24.56</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>24.56</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>1065.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>847.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>847.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>807.6</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>1097.52</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>1097.52</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-2.670018684602155</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>1065</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>1065.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>23.94</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>24.6</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>1168.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>998.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>998.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>742.5</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>1095.28</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>1095.28</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-19.14915290065665</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>1168</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>1168.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>23.97</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>24.41</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>24.63</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>24.63</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>701.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>863.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>863.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>670.1</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>1088.46</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>1088.46</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-53.04258917713958</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>701</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>701.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>42.4</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>42.48</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>43.14</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>42.48</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>43.14</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>13547622.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>14659168.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>14659168.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>17887034.9</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>18277901.48</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>18277901.48</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-547962.0252833553</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>13547622</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>13547622.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>42.17</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>43.13</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>43.13</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>12958802.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>16073079.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>16073079</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>18386657.0</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>18348897.3</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>18348897.3</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-286602.2072901838</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>12958802</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>12958802.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>42.07</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>42.55</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>43.14</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>43.14</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>18065170.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>21612161.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>21612161.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>18929302.0</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>18366436.22</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>18366436.22</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>160092.6115318537</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>18065170</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>18065170.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>41.98</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>42.6</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>43.15</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>43.15</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>16323007.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>21867625.8</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>21867625.8</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>19742012.9</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>18437817.12</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>18437817.12</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>245399.6165800616</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>16323007</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>16323007.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>42.06</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>42.7</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>43.17</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>43.17</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>12401240.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>21026069.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>21026069</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>19389188.6</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>18513222.28</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>18513222.28</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>545162.8160567805</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>12401240</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>12401240.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>42.18</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>42.82</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>43.18</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>42.82</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>43.18</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>20617176.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>21114901.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>21114901.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>19352673.9</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>18442352.46</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>18442352.46</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>1374115.179021496</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>20617176</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>20617176.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>42.3</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>42.93</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>43.2</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>42.93</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>43.2</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>40654214.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>20700235.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>20700235</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>18601984.5</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>18258352.18</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>18258352.18</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>1628978.441148892</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>40654214</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>40654214.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>42.4</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>43.04</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>43.2</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>43.2</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>19342492.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>16246442.6</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>16246442.6</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>15429165.8</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>17584761.88</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>17584761.88</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-211934.4858530071</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>19342492</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>19342492.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>42.44</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>43.14</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>43.2</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>43.2</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>12115223.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>17616400.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>17616400</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>16043074.8</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>17425113.3</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>17425113.3</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-550842.2213609666</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>12115223</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>12115223.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>42.48</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>43.23</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>43.2</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>43.2</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>12845403.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>17752308.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>17752308.2</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>17409247.6</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>17440215.86</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>17440215.86</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-240972.9427523017</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>12845403</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>12845403.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>42.56</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>43.34</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>43.19</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>43.34</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>43.19</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>18543843.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>17590446.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>17590446.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>17324539.3</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>17328707.66</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>17328707.66</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>132070.0603583716</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>18543843</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>18543843.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>

--- a/Result/checksun_type/農藥.xlsx
+++ b/Result/checksun_type/農藥.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ35"/>
+  <dimension ref="A1:CJ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14797,7 +14797,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>價_量;【d1】</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>1712</t>
@@ -14805,42 +14809,42 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>407.962</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -14850,37 +14854,37 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-22 00:00:00</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-23 00:00:00</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-15 00:00:00</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44.05</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -14890,12 +14894,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -14905,32 +14909,32 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.60</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr"/>
@@ -14946,269 +14950,4489 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>42.52</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>43.14</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>103.29</t>
         </is>
       </c>
       <c r="AQ35" t="n">
         <v>0</v>
       </c>
       <c r="AR35" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr">
+        <is>
+          <t>-109.76</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>52454485.41937765</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>17557368.0</t>
+        </is>
+      </c>
+      <c r="AX35" t="n">
+        <v>14794658.6</v>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>13349877.6</t>
+        </is>
+      </c>
+      <c r="AZ35" t="n">
+        <v>17690468.92</v>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>1444781</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>-571197.2076851345</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>-280370.5801276714</t>
+        </is>
+      </c>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>17557368.0</t>
+        </is>
+      </c>
+      <c r="BE35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF35" t="inlineStr">
+        <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="BG35" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BI35" t="inlineStr">
+        <is>
+          <t>興農</t>
+        </is>
+      </c>
+      <c r="BJ35" t="inlineStr">
+        <is>
+          <t>興農</t>
+        </is>
+      </c>
+      <c r="BK35" t="inlineStr">
+        <is>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="BL35" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM35" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="BN35" t="inlineStr">
+        <is>
+          <t>-7.517737364996673</t>
+        </is>
+      </c>
+      <c r="BO35" t="inlineStr">
+        <is>
+          <t>-8.363253652439093</t>
+        </is>
+      </c>
+      <c r="BP35" t="inlineStr">
+        <is>
+          <t>-2.89776970980012</t>
+        </is>
+      </c>
+      <c r="BQ35" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR35" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS35" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="BT35" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="BU35" t="inlineStr">
+        <is>
+          <t>10.40</t>
+        </is>
+      </c>
+      <c r="BV35" t="inlineStr">
+        <is>
+          <t>16.37</t>
+        </is>
+      </c>
+      <c r="BW35" t="inlineStr">
+        <is>
+          <t>30.98%</t>
+        </is>
+      </c>
+      <c r="BX35" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="BY35" t="inlineStr">
+        <is>
+          <t>47.54</t>
+        </is>
+      </c>
+      <c r="BZ35" t="inlineStr">
+        <is>
+          <t>18039</t>
+        </is>
+      </c>
+      <c r="CA35" t="inlineStr">
+        <is>
+          <t>植物保護58.00%、超市百貨23.00%、家用品及團膳14.00%、其他5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB35" t="inlineStr">
+        <is>
+          <t>興農-化學工業-上市</t>
+        </is>
+      </c>
+      <c r="CC35" t="inlineStr">
+        <is>
+          <t>化學工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD35" t="inlineStr">
+        <is>
+          <t>43.1</t>
+        </is>
+      </c>
+      <c r="CE35" t="inlineStr">
+        <is>
+          <t>43.15</t>
+        </is>
+      </c>
+      <c r="CF35" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="CG35" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="CH35" t="inlineStr">
+        <is>
+          <t>19.64</t>
+        </is>
+      </c>
+      <c r="CI35" t="inlineStr">
+        <is>
+          <t>** 石化及塑橡膠 - 塑膠製品、農藥</t>
+        </is>
+      </c>
+      <c r="CJ35" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>300.775</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>43.05</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>5.92</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2025-10-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>44.4</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>44.05</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>-2.27</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>5.60</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>91.67</t>
+        </is>
+      </c>
+      <c r="AH36" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>42.85</t>
+        </is>
+      </c>
+      <c r="AM36" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>43.15</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>42.93</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>90.77</t>
+        </is>
+      </c>
+      <c r="AQ36" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr">
+        <is>
+          <t>-112.28</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>52454485.41937765</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>12985283.0</t>
+        </is>
+      </c>
+      <c r="AX36" t="n">
+        <v>14193627.4</v>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>13400657.8</t>
+        </is>
+      </c>
+      <c r="AZ36" t="n">
+        <v>18233593.04</v>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>792969</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>-624074.7763319459</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>-603677.7162653264</t>
+        </is>
+      </c>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>12985283.0</t>
+        </is>
+      </c>
+      <c r="BE36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF36" t="inlineStr">
+        <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="BG36" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="BI36" t="inlineStr">
+        <is>
+          <t>興農</t>
+        </is>
+      </c>
+      <c r="BJ36" t="inlineStr">
+        <is>
+          <t>興農</t>
+        </is>
+      </c>
+      <c r="BK36" t="inlineStr">
+        <is>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="BL36" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM36" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="BN36" t="inlineStr">
+        <is>
+          <t>-7.517737364996673</t>
+        </is>
+      </c>
+      <c r="BO36" t="inlineStr">
+        <is>
+          <t>-8.363253652439093</t>
+        </is>
+      </c>
+      <c r="BP36" t="inlineStr">
+        <is>
+          <t>-2.89776970980012</t>
+        </is>
+      </c>
+      <c r="BQ36" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR36" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS36" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="BT36" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="BU36" t="inlineStr">
+        <is>
+          <t>10.40</t>
+        </is>
+      </c>
+      <c r="BV36" t="inlineStr">
+        <is>
+          <t>16.37</t>
+        </is>
+      </c>
+      <c r="BW36" t="inlineStr">
+        <is>
+          <t>30.98%</t>
+        </is>
+      </c>
+      <c r="BX36" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="BY36" t="inlineStr">
+        <is>
+          <t>47.54</t>
+        </is>
+      </c>
+      <c r="BZ36" t="inlineStr">
+        <is>
+          <t>18039</t>
+        </is>
+      </c>
+      <c r="CA36" t="inlineStr">
+        <is>
+          <t>植物保護58.00%、超市百貨23.00%、家用品及團膳14.00%、其他5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB36" t="inlineStr">
+        <is>
+          <t>興農-化學工業-上市</t>
+        </is>
+      </c>
+      <c r="CC36" t="inlineStr">
+        <is>
+          <t>化學工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD36" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="CE36" t="inlineStr">
+        <is>
+          <t>43.35</t>
+        </is>
+      </c>
+      <c r="CF36" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="CG36" t="inlineStr">
+        <is>
+          <t>43.05</t>
+        </is>
+      </c>
+      <c r="CH36" t="inlineStr">
+        <is>
+          <t>19.64</t>
+        </is>
+      </c>
+      <c r="CI36" t="inlineStr">
+        <is>
+          <t>** 石化及塑橡膠 - 塑膠製品、農藥</t>
+        </is>
+      </c>
+      <c r="CJ36" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>420.647</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>42.95</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>-2.84</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2025-10-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>44.4</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>44.05</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>-2.50</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>7.84</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>88.16</t>
+        </is>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>-1.55</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>42.81</t>
+        </is>
+      </c>
+      <c r="AM37" t="n">
+        <v>42.48</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>43.15</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>42.92</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>69.42</t>
+        </is>
+      </c>
+      <c r="AQ37" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr">
+        <is>
+          <t>-115.07</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>52454485.41937765</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>18075999.0</t>
+        </is>
+      </c>
+      <c r="AX37" t="n">
+        <v>13345009.6</v>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>13734430.2</t>
+        </is>
+      </c>
+      <c r="AZ37" t="n">
+        <v>18408416.72</v>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>-389420</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>-627783.3327076948</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>-554118.8851667847</t>
+        </is>
+      </c>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>18075999.0</t>
+        </is>
+      </c>
+      <c r="BE37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF37" t="inlineStr">
+        <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="BG37" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="BI37" t="inlineStr">
+        <is>
+          <t>興農</t>
+        </is>
+      </c>
+      <c r="BJ37" t="inlineStr">
+        <is>
+          <t>興農</t>
+        </is>
+      </c>
+      <c r="BK37" t="inlineStr">
+        <is>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="BL37" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM37" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="BN37" t="inlineStr">
+        <is>
+          <t>-7.517737364996673</t>
+        </is>
+      </c>
+      <c r="BO37" t="inlineStr">
+        <is>
+          <t>-8.363253652439093</t>
+        </is>
+      </c>
+      <c r="BP37" t="inlineStr">
+        <is>
+          <t>-2.89776970980012</t>
+        </is>
+      </c>
+      <c r="BQ37" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR37" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS37" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="BT37" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="BU37" t="inlineStr">
+        <is>
+          <t>10.40</t>
+        </is>
+      </c>
+      <c r="BV37" t="inlineStr">
+        <is>
+          <t>16.37</t>
+        </is>
+      </c>
+      <c r="BW37" t="inlineStr">
+        <is>
+          <t>30.98%</t>
+        </is>
+      </c>
+      <c r="BX37" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="BY37" t="inlineStr">
+        <is>
+          <t>47.54</t>
+        </is>
+      </c>
+      <c r="BZ37" t="inlineStr">
+        <is>
+          <t>18039</t>
+        </is>
+      </c>
+      <c r="CA37" t="inlineStr">
+        <is>
+          <t>植物保護58.00%、超市百貨23.00%、家用品及團膳14.00%、其他5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB37" t="inlineStr">
+        <is>
+          <t>興農-化學工業-上市</t>
+        </is>
+      </c>
+      <c r="CC37" t="inlineStr">
+        <is>
+          <t>化學工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD37" t="inlineStr">
+        <is>
+          <t>42.7</t>
+        </is>
+      </c>
+      <c r="CE37" t="inlineStr">
+        <is>
+          <t>43.2</t>
+        </is>
+      </c>
+      <c r="CF37" t="inlineStr">
+        <is>
+          <t>42.7</t>
+        </is>
+      </c>
+      <c r="CG37" t="inlineStr">
+        <is>
+          <t>42.95</t>
+        </is>
+      </c>
+      <c r="CH37" t="inlineStr">
+        <is>
+          <t>19.64</t>
+        </is>
+      </c>
+      <c r="CI37" t="inlineStr">
+        <is>
+          <t>** 石化及塑橡膠 - 塑膠製品、農藥</t>
+        </is>
+      </c>
+      <c r="CJ37" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>351.752</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>42.7</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>-11.33</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2025-10-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>44.4</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>44.05</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>-3.06</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>6.55</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>83.81</t>
+        </is>
+      </c>
+      <c r="AH38" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>-1.54</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>42.79</t>
+        </is>
+      </c>
+      <c r="AM38" t="n">
+        <v>42.48</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>43.15</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>42.91</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>55.40</t>
+        </is>
+      </c>
+      <c r="AQ38" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr">
+        <is>
+          <t>-117.69</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>52454485.41937765</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>15092666.0</t>
+        </is>
+      </c>
+      <c r="AX38" t="n">
+        <v>11674740.4</v>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>13166954.3</t>
+        </is>
+      </c>
+      <c r="AZ38" t="n">
+        <v>18281049.32</v>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>-1492213</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>-641176.868624224</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>-1008964.45198434</t>
+        </is>
+      </c>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>15092666.0</t>
+        </is>
+      </c>
+      <c r="BE38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF38" t="inlineStr">
+        <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="BG38" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BI38" t="inlineStr">
+        <is>
+          <t>興農</t>
+        </is>
+      </c>
+      <c r="BJ38" t="inlineStr">
+        <is>
+          <t>興農</t>
+        </is>
+      </c>
+      <c r="BK38" t="inlineStr">
+        <is>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="BL38" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM38" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="BN38" t="inlineStr">
+        <is>
+          <t>-7.517737364996673</t>
+        </is>
+      </c>
+      <c r="BO38" t="inlineStr">
+        <is>
+          <t>-8.363253652439093</t>
+        </is>
+      </c>
+      <c r="BP38" t="inlineStr">
+        <is>
+          <t>-2.89776970980012</t>
+        </is>
+      </c>
+      <c r="BQ38" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR38" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS38" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="BT38" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="BU38" t="inlineStr">
+        <is>
+          <t>10.40</t>
+        </is>
+      </c>
+      <c r="BV38" t="inlineStr">
+        <is>
+          <t>16.37</t>
+        </is>
+      </c>
+      <c r="BW38" t="inlineStr">
+        <is>
+          <t>30.98%</t>
+        </is>
+      </c>
+      <c r="BX38" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="BY38" t="inlineStr">
+        <is>
+          <t>47.54</t>
+        </is>
+      </c>
+      <c r="BZ38" t="inlineStr">
+        <is>
+          <t>18039</t>
+        </is>
+      </c>
+      <c r="CA38" t="inlineStr">
+        <is>
+          <t>植物保護58.00%、超市百貨23.00%、家用品及團膳14.00%、其他5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB38" t="inlineStr">
+        <is>
+          <t>興農-化學工業-上市</t>
+        </is>
+      </c>
+      <c r="CC38" t="inlineStr">
+        <is>
+          <t>化學工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD38" t="inlineStr">
+        <is>
+          <t>42.8</t>
+        </is>
+      </c>
+      <c r="CE38" t="inlineStr">
+        <is>
+          <t>43.05</t>
+        </is>
+      </c>
+      <c r="CF38" t="inlineStr">
+        <is>
+          <t>42.7</t>
+        </is>
+      </c>
+      <c r="CG38" t="inlineStr">
+        <is>
+          <t>42.7</t>
+        </is>
+      </c>
+      <c r="CH38" t="inlineStr">
+        <is>
+          <t>19.64</t>
+        </is>
+      </c>
+      <c r="CI38" t="inlineStr">
+        <is>
+          <t>** 石化及塑橡膠 - 塑膠製品、農藥</t>
+        </is>
+      </c>
+      <c r="CJ38" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>239.226</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>42.8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>-17.16</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2025-10-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>44.4</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>44.05</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>-2.84</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>4.46</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>89.47</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>90.69</t>
+        </is>
+      </c>
+      <c r="AH39" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>-1.55</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>42.83</t>
+        </is>
+      </c>
+      <c r="AM39" t="n">
+        <v>42.48</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>43.15</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>54.13</t>
+        </is>
+      </c>
+      <c r="AQ39" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr">
+        <is>
+          <t>-120.14</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>52454485.41937765</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>10261977.0</t>
+        </is>
+      </c>
+      <c r="AX39" t="n">
+        <v>11365731.6</v>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>13719405.3</t>
+        </is>
+      </c>
+      <c r="AZ39" t="n">
+        <v>18155195.68</v>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>-2353673</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>-574306.3989223846</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>-1303066.567009978</t>
+        </is>
+      </c>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>10261977.0</t>
+        </is>
+      </c>
+      <c r="BE39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF39" t="inlineStr">
+        <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="BG39" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="BI39" t="inlineStr">
+        <is>
+          <t>興農</t>
+        </is>
+      </c>
+      <c r="BJ39" t="inlineStr">
+        <is>
+          <t>興農</t>
+        </is>
+      </c>
+      <c r="BK39" t="inlineStr">
+        <is>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="BL39" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM39" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="BN39" t="inlineStr">
+        <is>
+          <t>-7.517737364996673</t>
+        </is>
+      </c>
+      <c r="BO39" t="inlineStr">
+        <is>
+          <t>-8.363253652439093</t>
+        </is>
+      </c>
+      <c r="BP39" t="inlineStr">
+        <is>
+          <t>-2.89776970980012</t>
+        </is>
+      </c>
+      <c r="BQ39" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR39" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS39" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="BT39" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="BU39" t="inlineStr">
+        <is>
+          <t>10.40</t>
+        </is>
+      </c>
+      <c r="BV39" t="inlineStr">
+        <is>
+          <t>16.37</t>
+        </is>
+      </c>
+      <c r="BW39" t="inlineStr">
+        <is>
+          <t>30.98%</t>
+        </is>
+      </c>
+      <c r="BX39" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="BY39" t="inlineStr">
+        <is>
+          <t>47.54</t>
+        </is>
+      </c>
+      <c r="BZ39" t="inlineStr">
+        <is>
+          <t>18039</t>
+        </is>
+      </c>
+      <c r="CA39" t="inlineStr">
+        <is>
+          <t>植物保護58.00%、超市百貨23.00%、家用品及團膳14.00%、其他5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB39" t="inlineStr">
+        <is>
+          <t>興農-化學工業-上市</t>
+        </is>
+      </c>
+      <c r="CC39" t="inlineStr">
+        <is>
+          <t>化學工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD39" t="inlineStr">
+        <is>
+          <t>42.75</t>
+        </is>
+      </c>
+      <c r="CE39" t="inlineStr">
+        <is>
+          <t>43.05</t>
+        </is>
+      </c>
+      <c r="CF39" t="inlineStr">
+        <is>
+          <t>42.7</t>
+        </is>
+      </c>
+      <c r="CG39" t="inlineStr">
+        <is>
+          <t>42.8</t>
+        </is>
+      </c>
+      <c r="CH39" t="inlineStr">
+        <is>
+          <t>19.64</t>
+        </is>
+      </c>
+      <c r="CI39" t="inlineStr">
+        <is>
+          <t>** 石化及塑橡膠 - 塑膠製品、農藥</t>
+        </is>
+      </c>
+      <c r="CJ39" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>339.053</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>42.75</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>-28.96</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2025-10-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>44.4</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>44.05</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>-2.95</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>6.32</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>-0.70</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>86.96</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>92.75</t>
+        </is>
+      </c>
+      <c r="AH40" t="n">
         <v>0</v>
       </c>
-      <c r="AS35" t="inlineStr">
+      <c r="AI40" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>42.75</t>
+        </is>
+      </c>
+      <c r="AM40" t="n">
+        <v>42.48</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>43.15</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>42.88</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>47.90</t>
+        </is>
+      </c>
+      <c r="AQ40" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr">
+        <is>
+          <t>-122.86</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>52454485.41937765</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>14552212.0</t>
+        </is>
+      </c>
+      <c r="AX40" t="n">
+        <v>11905096.6</v>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>16758629.0</t>
+        </is>
+      </c>
+      <c r="AZ40" t="n">
+        <v>18174005.78</v>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>-4853532</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>-441804.5501791858</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>-1159100.532510536</t>
+        </is>
+      </c>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>14552212.0</t>
+        </is>
+      </c>
+      <c r="BE40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF40" t="inlineStr">
+        <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="BG40" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BI40" t="inlineStr">
+        <is>
+          <t>興農</t>
+        </is>
+      </c>
+      <c r="BJ40" t="inlineStr">
+        <is>
+          <t>興農</t>
+        </is>
+      </c>
+      <c r="BK40" t="inlineStr">
+        <is>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="BL40" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM40" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="BN40" t="inlineStr">
+        <is>
+          <t>-7.517737364996673</t>
+        </is>
+      </c>
+      <c r="BO40" t="inlineStr">
+        <is>
+          <t>-8.363253652439093</t>
+        </is>
+      </c>
+      <c r="BP40" t="inlineStr">
+        <is>
+          <t>-2.89776970980012</t>
+        </is>
+      </c>
+      <c r="BQ40" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR40" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS40" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="BT40" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="BU40" t="inlineStr">
+        <is>
+          <t>10.40</t>
+        </is>
+      </c>
+      <c r="BV40" t="inlineStr">
+        <is>
+          <t>16.37</t>
+        </is>
+      </c>
+      <c r="BW40" t="inlineStr">
+        <is>
+          <t>30.98%</t>
+        </is>
+      </c>
+      <c r="BX40" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="BY40" t="inlineStr">
+        <is>
+          <t>47.54</t>
+        </is>
+      </c>
+      <c r="BZ40" t="inlineStr">
+        <is>
+          <t>18039</t>
+        </is>
+      </c>
+      <c r="CA40" t="inlineStr">
+        <is>
+          <t>植物保護58.00%、超市百貨23.00%、家用品及團膳14.00%、其他5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB40" t="inlineStr">
+        <is>
+          <t>興農-化學工業-上市</t>
+        </is>
+      </c>
+      <c r="CC40" t="inlineStr">
+        <is>
+          <t>化學工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD40" t="inlineStr">
+        <is>
+          <t>42.7</t>
+        </is>
+      </c>
+      <c r="CE40" t="inlineStr">
+        <is>
+          <t>43.1</t>
+        </is>
+      </c>
+      <c r="CF40" t="inlineStr">
+        <is>
+          <t>42.7</t>
+        </is>
+      </c>
+      <c r="CG40" t="inlineStr">
+        <is>
+          <t>42.75</t>
+        </is>
+      </c>
+      <c r="CH40" t="inlineStr">
+        <is>
+          <t>19.64</t>
+        </is>
+      </c>
+      <c r="CI40" t="inlineStr">
+        <is>
+          <t>** 石化及塑橡膠 - 塑膠製品、農藥</t>
+        </is>
+      </c>
+      <c r="CJ40" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AT35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AX35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BC35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BG35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BH35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BI35" t="inlineStr">
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>203.779</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>42.85</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>-26.86</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2025-10-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>44.4</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>44.05</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>-2.72</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>95.65</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>97.1</t>
+        </is>
+      </c>
+      <c r="AH41" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>42.73</t>
+        </is>
+      </c>
+      <c r="AM41" t="n">
+        <v>42.48</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>42.87</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>42.94</t>
+        </is>
+      </c>
+      <c r="AQ41" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr">
+        <is>
+          <t>-125.60</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>52454485.41937765</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>8742194.0</t>
+        </is>
+      </c>
+      <c r="AX41" t="n">
+        <v>12607688.2</v>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>17237657.0</t>
+        </is>
+      </c>
+      <c r="AZ41" t="n">
+        <v>18118005.16</v>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>-4629968</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>-311387.0988462131</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>-1371706.357064527</t>
+        </is>
+      </c>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>8742194.0</t>
+        </is>
+      </c>
+      <c r="BE41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF41" t="inlineStr">
+        <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="BG41" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="BI41" t="inlineStr">
         <is>
           <t>興農</t>
         </is>
       </c>
-      <c r="BJ35" t="inlineStr">
+      <c r="BJ41" t="inlineStr">
         <is>
           <t>興農</t>
         </is>
       </c>
-      <c r="BK35" t="inlineStr">
+      <c r="BK41" t="inlineStr">
         <is>
           <t>化學工業</t>
         </is>
       </c>
-      <c r="BL35" t="inlineStr">
+      <c r="BL41" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM35" t="inlineStr">
+      <c r="BM41" t="inlineStr">
         <is>
           <t>0.32</t>
         </is>
       </c>
-      <c r="BN35" t="inlineStr">
+      <c r="BN41" t="inlineStr">
         <is>
           <t>-7.517737364996673</t>
         </is>
       </c>
-      <c r="BO35" t="inlineStr">
+      <c r="BO41" t="inlineStr">
         <is>
           <t>-8.363253652439093</t>
         </is>
       </c>
-      <c r="BP35" t="inlineStr">
+      <c r="BP41" t="inlineStr">
         <is>
           <t>-2.89776970980012</t>
         </is>
       </c>
-      <c r="BQ35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR35" t="inlineStr">
+      <c r="BQ41" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR41" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS35" t="inlineStr">
+      <c r="BS41" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="BT41" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="BU41" t="inlineStr">
+        <is>
+          <t>10.40</t>
+        </is>
+      </c>
+      <c r="BV41" t="inlineStr">
+        <is>
+          <t>16.37</t>
+        </is>
+      </c>
+      <c r="BW41" t="inlineStr">
+        <is>
+          <t>30.98%</t>
+        </is>
+      </c>
+      <c r="BX41" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="BY41" t="inlineStr">
+        <is>
+          <t>47.54</t>
+        </is>
+      </c>
+      <c r="BZ41" t="inlineStr">
+        <is>
+          <t>18039</t>
+        </is>
+      </c>
+      <c r="CA41" t="inlineStr">
+        <is>
+          <t>植物保護58.00%、超市百貨23.00%、家用品及團膳14.00%、其他5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB41" t="inlineStr">
+        <is>
+          <t>興農-化學工業-上市</t>
+        </is>
+      </c>
+      <c r="CC41" t="inlineStr">
+        <is>
+          <t>化學工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD41" t="inlineStr">
+        <is>
+          <t>42.85</t>
+        </is>
+      </c>
+      <c r="CE41" t="inlineStr">
+        <is>
+          <t>43.0</t>
+        </is>
+      </c>
+      <c r="CF41" t="inlineStr">
+        <is>
+          <t>42.8</t>
+        </is>
+      </c>
+      <c r="CG41" t="inlineStr">
+        <is>
+          <t>42.85</t>
+        </is>
+      </c>
+      <c r="CH41" t="inlineStr">
+        <is>
+          <t>19.64</t>
+        </is>
+      </c>
+      <c r="CI41" t="inlineStr">
+        <is>
+          <t>** 石化及塑橡膠 - 塑膠製品、農藥</t>
+        </is>
+      </c>
+      <c r="CJ41" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>226.807</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>42.85</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>-19.64</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2025-10-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>44.4</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>44.05</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>-2.72</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>95.65</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>89.29</t>
+        </is>
+      </c>
+      <c r="AH42" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>-1.55</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>42.58</t>
+        </is>
+      </c>
+      <c r="AM42" t="n">
+        <v>42.47</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>42.85</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>33.24</t>
+        </is>
+      </c>
+      <c r="AQ42" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr">
+        <is>
+          <t>-128.35</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>52454485.41937765</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>9724653.0</t>
+        </is>
+      </c>
+      <c r="AX42" t="n">
+        <v>14123850.8</v>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>17574959.9</t>
+        </is>
+      </c>
+      <c r="AZ42" t="n">
+        <v>18197434.86</v>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>-3451109</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>-118601.779170156</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>-1003937.522246493</t>
+        </is>
+      </c>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>9724653.0</t>
+        </is>
+      </c>
+      <c r="BE42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF42" t="inlineStr">
+        <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="BG42" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="BI42" t="inlineStr">
+        <is>
+          <t>興農</t>
+        </is>
+      </c>
+      <c r="BJ42" t="inlineStr">
+        <is>
+          <t>興農</t>
+        </is>
+      </c>
+      <c r="BK42" t="inlineStr">
+        <is>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="BL42" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM42" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="BN42" t="inlineStr">
+        <is>
+          <t>-7.517737364996673</t>
+        </is>
+      </c>
+      <c r="BO42" t="inlineStr">
+        <is>
+          <t>-8.363253652439093</t>
+        </is>
+      </c>
+      <c r="BP42" t="inlineStr">
+        <is>
+          <t>-2.89776970980012</t>
+        </is>
+      </c>
+      <c r="BQ42" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR42" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS42" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="BT42" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="BU42" t="inlineStr">
+        <is>
+          <t>10.40</t>
+        </is>
+      </c>
+      <c r="BV42" t="inlineStr">
+        <is>
+          <t>16.37</t>
+        </is>
+      </c>
+      <c r="BW42" t="inlineStr">
+        <is>
+          <t>30.98%</t>
+        </is>
+      </c>
+      <c r="BX42" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="BY42" t="inlineStr">
+        <is>
+          <t>47.54</t>
+        </is>
+      </c>
+      <c r="BZ42" t="inlineStr">
+        <is>
+          <t>18039</t>
+        </is>
+      </c>
+      <c r="CA42" t="inlineStr">
+        <is>
+          <t>植物保護58.00%、超市百貨23.00%、家用品及團膳14.00%、其他5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB42" t="inlineStr">
+        <is>
+          <t>興農-化學工業-上市</t>
+        </is>
+      </c>
+      <c r="CC42" t="inlineStr">
+        <is>
+          <t>化學工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD42" t="inlineStr">
+        <is>
+          <t>42.6</t>
+        </is>
+      </c>
+      <c r="CE42" t="inlineStr">
+        <is>
+          <t>43.2</t>
+        </is>
+      </c>
+      <c r="CF42" t="inlineStr">
+        <is>
+          <t>42.6</t>
+        </is>
+      </c>
+      <c r="CG42" t="inlineStr">
+        <is>
+          <t>42.85</t>
+        </is>
+      </c>
+      <c r="CH42" t="inlineStr">
+        <is>
+          <t>19.64</t>
+        </is>
+      </c>
+      <c r="CI42" t="inlineStr">
+        <is>
+          <t>** 石化及塑橡膠 - 塑膠製品、農藥</t>
+        </is>
+      </c>
+      <c r="CJ42" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>317.132</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-18.05</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2025-10-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>44.4</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>44.05</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>-2.61</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>5.91</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>90.74</t>
+        </is>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>-1.52</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="AM43" t="n">
+        <v>42.48</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>42.82</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>21.31</t>
+        </is>
+      </c>
+      <c r="AQ43" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr">
+        <is>
+          <t>-130.70</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>52454485.41937765</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>13547622.0</t>
+        </is>
+      </c>
+      <c r="AX43" t="n">
+        <v>14659168.2</v>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>17887034.9</t>
+        </is>
+      </c>
+      <c r="AZ43" t="n">
+        <v>18277901.48</v>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>-3227866</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>42368.35593463251</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>-547962.0252833553</t>
+        </is>
+      </c>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>13547622.0</t>
+        </is>
+      </c>
+      <c r="BE43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF43" t="inlineStr">
+        <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="BG43" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BI43" t="inlineStr">
+        <is>
+          <t>興農</t>
+        </is>
+      </c>
+      <c r="BJ43" t="inlineStr">
+        <is>
+          <t>興農</t>
+        </is>
+      </c>
+      <c r="BK43" t="inlineStr">
+        <is>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="BL43" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM43" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="BN43" t="inlineStr">
+        <is>
+          <t>-7.517737364996673</t>
+        </is>
+      </c>
+      <c r="BO43" t="inlineStr">
+        <is>
+          <t>-8.363253652439093</t>
+        </is>
+      </c>
+      <c r="BP43" t="inlineStr">
+        <is>
+          <t>-2.89776970980012</t>
+        </is>
+      </c>
+      <c r="BQ43" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR43" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS43" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="BT43" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="BU43" t="inlineStr">
+        <is>
+          <t>10.40</t>
+        </is>
+      </c>
+      <c r="BV43" t="inlineStr">
+        <is>
+          <t>16.37</t>
+        </is>
+      </c>
+      <c r="BW43" t="inlineStr">
+        <is>
+          <t>30.98%</t>
+        </is>
+      </c>
+      <c r="BX43" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="BY43" t="inlineStr">
+        <is>
+          <t>47.54</t>
+        </is>
+      </c>
+      <c r="BZ43" t="inlineStr">
+        <is>
+          <t>18039</t>
+        </is>
+      </c>
+      <c r="CA43" t="inlineStr">
+        <is>
+          <t>植物保護58.00%、超市百貨23.00%、家用品及團膳14.00%、其他5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB43" t="inlineStr">
+        <is>
+          <t>興農-化學工業-上市</t>
+        </is>
+      </c>
+      <c r="CC43" t="inlineStr">
+        <is>
+          <t>化學工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD43" t="inlineStr">
+        <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="CE43" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="CF43" t="inlineStr">
+        <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="CG43" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="CH43" t="inlineStr">
+        <is>
+          <t>19.64</t>
+        </is>
+      </c>
+      <c r="CI43" t="inlineStr">
+        <is>
+          <t>** 石化及塑橡膠 - 塑膠製品、農藥</t>
+        </is>
+      </c>
+      <c r="CJ43" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>-0.59</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>305.767</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>-12.58</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2025-10-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>44.4</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>44.05</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>-3.75</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="BT35" t="inlineStr">
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>72.22</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>71.99</t>
+        </is>
+      </c>
+      <c r="AH44" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>42.17</t>
+        </is>
+      </c>
+      <c r="AM44" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>43.13</v>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>42.8</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="AQ44" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr">
+        <is>
+          <t>-132.34</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>52454485.41937765</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>12958802.0</t>
+        </is>
+      </c>
+      <c r="AX44" t="n">
+        <v>16073079</v>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>18386657.0</t>
+        </is>
+      </c>
+      <c r="AZ44" t="n">
+        <v>18348897.3</v>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>-2313578</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>149701.1525197212</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>-286602.2072901838</t>
+        </is>
+      </c>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>12958802.0</t>
+        </is>
+      </c>
+      <c r="BE44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF44" t="inlineStr">
+        <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="BG44" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="BI44" t="inlineStr">
+        <is>
+          <t>興農</t>
+        </is>
+      </c>
+      <c r="BJ44" t="inlineStr">
+        <is>
+          <t>興農</t>
+        </is>
+      </c>
+      <c r="BK44" t="inlineStr">
+        <is>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="BL44" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM44" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="BN44" t="inlineStr">
+        <is>
+          <t>-7.517737364996673</t>
+        </is>
+      </c>
+      <c r="BO44" t="inlineStr">
+        <is>
+          <t>-8.363253652439093</t>
+        </is>
+      </c>
+      <c r="BP44" t="inlineStr">
+        <is>
+          <t>-2.89776970980012</t>
+        </is>
+      </c>
+      <c r="BQ44" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR44" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS44" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="BT44" t="inlineStr">
         <is>
           <t>5.83</t>
         </is>
       </c>
-      <c r="BU35" t="inlineStr">
+      <c r="BU44" t="inlineStr">
         <is>
           <t>10.40</t>
         </is>
       </c>
-      <c r="BV35" t="inlineStr">
+      <c r="BV44" t="inlineStr">
         <is>
           <t>16.37</t>
         </is>
       </c>
-      <c r="BW35" t="inlineStr">
+      <c r="BW44" t="inlineStr">
         <is>
           <t>30.98%</t>
         </is>
       </c>
-      <c r="BX35" t="inlineStr">
+      <c r="BX44" t="inlineStr">
         <is>
           <t>5.91%</t>
         </is>
       </c>
-      <c r="BY35" t="inlineStr">
+      <c r="BY44" t="inlineStr">
         <is>
           <t>47.54</t>
         </is>
       </c>
-      <c r="BZ35" t="inlineStr">
+      <c r="BZ44" t="inlineStr">
         <is>
           <t>18039</t>
         </is>
       </c>
-      <c r="CA35" t="inlineStr">
+      <c r="CA44" t="inlineStr">
         <is>
           <t>植物保護58.00%、超市百貨23.00%、家用品及團膳14.00%、其他5.00% (2024年)</t>
         </is>
       </c>
-      <c r="CB35" t="inlineStr">
+      <c r="CB44" t="inlineStr">
         <is>
           <t>興農-化學工業-上市</t>
         </is>
       </c>
-      <c r="CC35" t="inlineStr">
-        <is>
-          <t>化學工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE35" t="inlineStr">
+      <c r="CC44" t="inlineStr">
+        <is>
+          <t>化學工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD44" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="CE44" t="inlineStr">
+        <is>
+          <t>42.6</t>
+        </is>
+      </c>
+      <c r="CF44" t="inlineStr">
+        <is>
+          <t>42.2</t>
+        </is>
+      </c>
+      <c r="CG44" t="inlineStr">
+        <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="CH44" t="inlineStr">
+        <is>
+          <t>19.64</t>
+        </is>
+      </c>
+      <c r="CI44" t="inlineStr">
+        <is>
+          <t>** 石化及塑橡膠 - 塑膠製品、農藥</t>
+        </is>
+      </c>
+      <c r="CJ44" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>426.026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>42.65</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CF35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CG35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CH35" t="inlineStr">
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>14.17</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2025-10-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>44.4</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>44.05</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>-3.18</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>7.94</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>56.25</t>
+        </is>
+      </c>
+      <c r="AH45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>-1.38</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>42.07</t>
+        </is>
+      </c>
+      <c r="AM45" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>42.78</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>-3.84</t>
+        </is>
+      </c>
+      <c r="AQ45" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr">
+        <is>
+          <t>-132.66</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>52454485.41937765</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>18065170.0</t>
+        </is>
+      </c>
+      <c r="AX45" t="n">
+        <v>21612161.4</v>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>18929302.0</t>
+        </is>
+      </c>
+      <c r="AZ45" t="n">
+        <v>18366436.22</v>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>2682859</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>229029.0361215221</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>160092.6115318537</t>
+        </is>
+      </c>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>18065170.0</t>
+        </is>
+      </c>
+      <c r="BE45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF45" t="inlineStr">
+        <is>
+          <t>42.4</t>
+        </is>
+      </c>
+      <c r="BG45" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="BH45" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="BI45" t="inlineStr">
+        <is>
+          <t>興農</t>
+        </is>
+      </c>
+      <c r="BJ45" t="inlineStr">
+        <is>
+          <t>興農</t>
+        </is>
+      </c>
+      <c r="BK45" t="inlineStr">
+        <is>
+          <t>化學工業</t>
+        </is>
+      </c>
+      <c r="BL45" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM45" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="BN45" t="inlineStr">
+        <is>
+          <t>-7.517737364996673</t>
+        </is>
+      </c>
+      <c r="BO45" t="inlineStr">
+        <is>
+          <t>-8.363253652439093</t>
+        </is>
+      </c>
+      <c r="BP45" t="inlineStr">
+        <is>
+          <t>-2.89776970980012</t>
+        </is>
+      </c>
+      <c r="BQ45" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR45" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS45" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="BT45" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="BU45" t="inlineStr">
+        <is>
+          <t>10.40</t>
+        </is>
+      </c>
+      <c r="BV45" t="inlineStr">
+        <is>
+          <t>16.37</t>
+        </is>
+      </c>
+      <c r="BW45" t="inlineStr">
+        <is>
+          <t>30.98%</t>
+        </is>
+      </c>
+      <c r="BX45" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="BY45" t="inlineStr">
+        <is>
+          <t>47.54</t>
+        </is>
+      </c>
+      <c r="BZ45" t="inlineStr">
+        <is>
+          <t>18039</t>
+        </is>
+      </c>
+      <c r="CA45" t="inlineStr">
+        <is>
+          <t>植物保護58.00%、超市百貨23.00%、家用品及團膳14.00%、其他5.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB45" t="inlineStr">
+        <is>
+          <t>興農-化學工業-上市</t>
+        </is>
+      </c>
+      <c r="CC45" t="inlineStr">
+        <is>
+          <t>化學工業右上上市</t>
+        </is>
+      </c>
+      <c r="CD45" t="inlineStr">
+        <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="CE45" t="inlineStr">
+        <is>
+          <t>42.65</t>
+        </is>
+      </c>
+      <c r="CF45" t="inlineStr">
+        <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="CG45" t="inlineStr">
+        <is>
+          <t>42.65</t>
+        </is>
+      </c>
+      <c r="CH45" t="inlineStr">
         <is>
           <t>19.64</t>
         </is>
       </c>
-      <c r="CI35" t="inlineStr">
+      <c r="CI45" t="inlineStr">
         <is>
           <t>** 石化及塑橡膠 - 塑膠製品、農藥</t>
         </is>
       </c>
-      <c r="CJ35" t="inlineStr">
+      <c r="CJ45" t="inlineStr">
         <is>
           <t>False</t>
         </is>
